--- a/extenbooks/XS2001_extenbook.xlsx
+++ b/extenbooks/XS2001_extenbook.xlsx
@@ -1674,14 +1674,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="B16" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-circ-constant_capital</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1697,14 +1697,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1947</v>
+        <v>1963</v>
       </c>
       <c r="B17" t="n">
-        <v>0.32</v>
+        <v>1.03</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-circ-constant_capital</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1720,14 +1720,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1947</v>
+        <v>1967</v>
       </c>
       <c r="B18" t="n">
-        <v>0.32</v>
+        <v>1.04</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs_over_R</t>
+          <t>XS2001-circ-constant_capital</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1743,14 +1743,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="B19" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-circ-constant_capital</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1766,14 +1766,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1947</v>
+        <v>1998</v>
       </c>
       <c r="B20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-circ-constant_capital</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1792,11 +1792,11 @@
         <v>1947</v>
       </c>
       <c r="B21" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1812,14 +1812,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XS2001-circ-value_added</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1835,14 +1835,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1947</v>
+        <v>1963</v>
       </c>
       <c r="B23" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1858,14 +1858,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1947</v>
+        <v>1967</v>
       </c>
       <c r="B24" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1881,14 +1881,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="B25" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XS2001-fixed-max_rate_profit_R</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1904,14 +1904,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1947</v>
+        <v>1998</v>
       </c>
       <c r="B26" t="n">
-        <v>0.24</v>
+        <v>0.96</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-circ-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1930,11 +1930,11 @@
         <v>1947</v>
       </c>
       <c r="B27" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1950,14 +1950,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="B28" t="n">
-        <v>1.04</v>
+        <v>0.32</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1973,14 +1973,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1947</v>
+        <v>1963</v>
       </c>
       <c r="B29" t="n">
-        <v>0.99</v>
+        <v>0.36</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_surplus_value</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1996,14 +1996,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1947</v>
+        <v>1967</v>
       </c>
       <c r="B30" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2019,14 +2019,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="B31" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2042,14 +2042,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1947</v>
+        <v>1998</v>
       </c>
       <c r="B32" t="n">
-        <v>0.98</v>
+        <v>0.23</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XS2001-fixed-variable_capital</t>
+          <t>XS2001-circ-r_obs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2065,14 +2065,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1958</v>
+        <v>1947</v>
       </c>
       <c r="B33" t="n">
-        <v>1.02</v>
+        <v>0.32</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>XS2001-circ-constant_capital</t>
+          <t>XS2001-circ-r_obs_over_R</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2091,11 +2091,11 @@
         <v>1958</v>
       </c>
       <c r="B34" t="n">
-        <v>0.96</v>
+        <v>0.3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-circ-r_obs_over_R</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2111,14 +2111,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="B35" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-circ-r_obs_over_R</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2157,14 +2157,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B37" t="n">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-circ-r_obs_over_R</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2180,14 +2180,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1958</v>
+        <v>1998</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-circ-r_obs_over_R</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2203,14 +2203,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1958</v>
+        <v>1947</v>
       </c>
       <c r="B39" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2229,11 +2229,11 @@
         <v>1958</v>
       </c>
       <c r="B40" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XS2001-circ-value_added</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2249,14 +2249,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="B41" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2272,14 +2272,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="B42" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2295,14 +2295,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B43" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>XS2001-fixed-max_rate_profit_R</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2318,14 +2318,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1958</v>
+        <v>1998</v>
       </c>
       <c r="B44" t="n">
-        <v>0.18</v>
+        <v>0.96</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-circ-rate_profit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2341,14 +2341,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1958</v>
+        <v>1947</v>
       </c>
       <c r="B45" t="n">
-        <v>0.26</v>
+        <v>1.03</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2367,11 +2367,11 @@
         <v>1958</v>
       </c>
       <c r="B46" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2387,14 +2387,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="B47" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_surplus_value</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2410,14 +2410,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="B48" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2433,14 +2433,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B49" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2456,14 +2456,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1958</v>
+        <v>1998</v>
       </c>
       <c r="B50" t="n">
         <v>0.99</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>XS2001-fixed-variable_capital</t>
+          <t>XS2001-circ-rate_surplus_value</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2479,14 +2479,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1963</v>
+        <v>1947</v>
       </c>
       <c r="B51" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>XS2001-circ-constant_capital</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2502,14 +2502,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="B52" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2528,11 +2528,11 @@
         <v>1963</v>
       </c>
       <c r="B53" t="n">
-        <v>0.36</v>
+        <v>0.97</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2548,14 +2548,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="B54" t="n">
-        <v>0.35</v>
+        <v>0.97</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs_over_R</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2571,14 +2571,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="B55" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2594,14 +2594,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-circ-surplus_value</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2617,14 +2617,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1963</v>
+        <v>1947</v>
       </c>
       <c r="B57" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-circ-value_added</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="B58" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-circ-value_added</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2686,14 +2686,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="B60" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-circ-value_added</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2709,14 +2709,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="B61" t="n">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>XS2001-fixed-max_rate_profit_R</t>
+          <t>XS2001-circ-value_added</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2732,14 +2732,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="B62" t="n">
-        <v>0.21</v>
+        <v>0.98</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-circ-value_added</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2755,14 +2755,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1963</v>
+        <v>1947</v>
       </c>
       <c r="B63" t="n">
-        <v>0.28</v>
+        <v>0.99</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2778,14 +2778,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="B64" t="n">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_surplus_value</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2824,14 +2824,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="B66" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2847,14 +2847,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="B67" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2870,14 +2870,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="B68" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>XS2001-fixed-variable_capital</t>
+          <t>XS2001-circ-variable_capital</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2893,14 +2893,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1967</v>
+        <v>1947</v>
       </c>
       <c r="B69" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>XS2001-circ-constant_capital</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2916,14 +2916,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="B70" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2939,14 +2939,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="B71" t="n">
-        <v>0.4</v>
+        <v>1.04</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2965,11 +2965,11 @@
         <v>1967</v>
       </c>
       <c r="B72" t="n">
-        <v>0.39</v>
+        <v>1.04</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs_over_R</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2985,14 +2985,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="B73" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3008,14 +3008,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1967</v>
+        <v>1998</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-fixed-constant_capital</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3031,14 +3031,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1967</v>
+        <v>1947</v>
       </c>
       <c r="B75" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3054,14 +3054,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="B76" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XS2001-circ-value_added</t>
+          <t>XS2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3077,14 +3077,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="B77" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3103,11 +3103,11 @@
         <v>1967</v>
       </c>
       <c r="B78" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="B79" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3146,14 +3146,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1967</v>
+        <v>1998</v>
       </c>
       <c r="B80" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3169,14 +3169,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1967</v>
+        <v>1947</v>
       </c>
       <c r="B81" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3192,14 +3192,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="B82" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3215,14 +3215,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="B83" t="n">
-        <v>0.96</v>
+        <v>0.21</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_surplus_value</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3241,11 +3241,11 @@
         <v>1967</v>
       </c>
       <c r="B84" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3261,14 +3261,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="B85" t="n">
-        <v>0.97</v>
+        <v>0.19</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3284,14 +3284,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1967</v>
+        <v>1998</v>
       </c>
       <c r="B86" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>XS2001-fixed-variable_capital</t>
+          <t>XS2001-fixed-r_obs</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3307,14 +3307,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1972</v>
+        <v>1947</v>
       </c>
       <c r="B87" t="n">
-        <v>1.03</v>
+        <v>0.29</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>XS2001-circ-constant_capital</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3330,14 +3330,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="B88" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3353,14 +3353,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1972</v>
+        <v>1963</v>
       </c>
       <c r="B89" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3376,14 +3376,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="B90" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs_over_R</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3402,11 +3402,11 @@
         <v>1972</v>
       </c>
       <c r="B91" t="n">
-        <v>0.95</v>
+        <v>0.28</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3422,14 +3422,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="B92" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-fixed-r_obs_over_R</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3445,14 +3445,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1972</v>
+        <v>1947</v>
       </c>
       <c r="B93" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3468,14 +3468,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="B94" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>XS2001-circ-value_added</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3491,14 +3491,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1972</v>
+        <v>1963</v>
       </c>
       <c r="B95" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3514,14 +3514,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="B96" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3540,11 +3540,11 @@
         <v>1972</v>
       </c>
       <c r="B97" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS2001-fixed-max_rate_profit_R</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3560,14 +3560,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="B98" t="n">
-        <v>0.19</v>
+        <v>0.98</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-fixed-rate_profit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3583,14 +3583,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1972</v>
+        <v>1947</v>
       </c>
       <c r="B99" t="n">
-        <v>0.28</v>
+        <v>0.99</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-fixed-rate_surplus_value</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3606,14 +3606,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="B100" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-fixed-rate_surplus_value</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1972</v>
+        <v>1963</v>
       </c>
       <c r="B101" t="n">
         <v>0.97</v>
@@ -3652,14 +3652,14 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="B102" t="n">
         <v>0.96</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-fixed-rate_surplus_value</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-fixed-rate_surplus_value</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3698,14 +3698,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="B104" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS2001-fixed-variable_capital</t>
+          <t>XS2001-fixed-rate_surplus_value</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3721,14 +3721,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1998</v>
+        <v>1947</v>
       </c>
       <c r="B105" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>XS2001-circ-constant_capital</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3744,14 +3744,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1998</v>
+        <v>1958</v>
       </c>
       <c r="B106" t="n">
         <v>0.96</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS2001-circ-max_rate_profit_R</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3767,14 +3767,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1998</v>
+        <v>1963</v>
       </c>
       <c r="B107" t="n">
-        <v>0.23</v>
+        <v>0.95</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3790,14 +3790,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1998</v>
+        <v>1967</v>
       </c>
       <c r="B108" t="n">
-        <v>0.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>XS2001-circ-r_obs_over_R</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3813,14 +3813,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B109" t="n">
         <v>0.96</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_profit</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3839,11 +3839,11 @@
         <v>1998</v>
       </c>
       <c r="B110" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS2001-circ-rate_surplus_value</t>
+          <t>XS2001-fixed-surplus_value</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3859,14 +3859,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1998</v>
+        <v>1947</v>
       </c>
       <c r="B111" t="n">
         <v>0.98</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>XS2001-circ-surplus_value</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3882,14 +3882,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1998</v>
+        <v>1958</v>
       </c>
       <c r="B112" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS2001-circ-value_added</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3905,14 +3905,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1998</v>
+        <v>1963</v>
       </c>
       <c r="B113" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS2001-circ-variable_capital</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3928,14 +3928,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1998</v>
+        <v>1967</v>
       </c>
       <c r="B114" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>XS2001-fixed-constant_capital</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3951,14 +3951,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS2001-fixed-max_rate_profit_R</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3977,11 +3977,11 @@
         <v>1998</v>
       </c>
       <c r="B116" t="n">
-        <v>0.11</v>
+        <v>0.96</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs</t>
+          <t>XS2001-fixed-value_added</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3997,14 +3997,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1998</v>
+        <v>1947</v>
       </c>
       <c r="B117" t="n">
-        <v>0.27</v>
+        <v>0.98</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>XS2001-fixed-r_obs_over_R</t>
+          <t>XS2001-fixed-variable_capital</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4020,14 +4020,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1998</v>
+        <v>1958</v>
       </c>
       <c r="B118" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_profit</t>
+          <t>XS2001-fixed-variable_capital</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4043,14 +4043,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1998</v>
+        <v>1963</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS2001-fixed-rate_surplus_value</t>
+          <t>XS2001-fixed-variable_capital</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4066,14 +4066,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1998</v>
+        <v>1967</v>
       </c>
       <c r="B120" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>XS2001-fixed-surplus_value</t>
+          <t>XS2001-fixed-variable_capital</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4089,14 +4089,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B121" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS2001-fixed-value_added</t>
+          <t>XS2001-fixed-variable_capital</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A185"/>
+  <dimension ref="A1:A189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4184,42 +4184,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: XS2001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: XS2001</t>
+          <t>**Content type**: `time_series` (aggregate-ratio panel)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Content type**: `time_series` (aggregate-ratio panel)</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: study_complete</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-fanout-ES</t>
+          <t>This series was previously catalogued under the identifier ES2001.</t>
         </is>
       </c>
     </row>
@@ -4246,227 +4242,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>of profit, for two Sraffa-price models (circulating and fixed capital),</t>
+          <t>of profit, for two Sraffa-price models (Sraffa prices are production</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>across the six US BEA benchmark IO years Shaikh (2020) covers:</t>
+          <t>prices derived from an economy's input-output structure; the two models</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1947, 1958, 1963, 1967, 1972, 1998. Source: Shaikh (2020) "An</t>
+          <t>use circulating capital and fixed capital), across the six US</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Empirically Sufficient Form for Sraffa Prices", Tables 1 and 2</t>
+          <t>input-output (IO) benchmark years from the US Bureau of Economic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(paper p. 10).</t>
+          <t>Analysis (BEA) that Shaikh (2020) covers:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1947, 1958, 1963, 1967, 1972, 1998. Source: Shaikh (2020) "An</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>The panel has 12 rows (2 models × 6 years), each carrying nine</t>
+          <t>Empirically Sufficient Form for Sraffa Prices", Tables 1 and 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>aggregate ratios (r_obs, r_obs/R, constant capital, variable capital,</t>
+          <t>(paper p. 10).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>surplus value, value added, rate of surplus value, rate of profit,</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>maximum rate R). All ratios fall in [0.94, 1.08].</t>
+          <t>The panel has 12 rows (2 models × 6 years), each carrying nine</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aggregate ratios (r_obs, r_obs/R, constant capital, variable capital,</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>surplus value, value added, rate of surplus value, rate of profit,</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>maximum rate of profit R). All ratios fall in [0.94, 1.08].</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>The Tables-1/2 panel is the paper's empirical evidence for the</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>**Sraffa Stochastic Effect** (SSE): statistical compensation of large</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>numbers makes price and labor-value aggregates essentially identical</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>across all 6 benchmark years and both capital-stock models. This is</t>
+          <t>The Tables-1/2 panel is the paper's empirical evidence for the</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>the time-series content of the paper.</t>
+          <t>**Sraffa Stochastic Effect** (SSE): statistical compensation of large</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>numbers makes price and labor-value aggregates essentially identical</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The paper's Figures 1-9 — illustrative 403-sector Sraffa price-value</t>
+          <t>across all 6 benchmark years and both capital-stock models. This is</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>curves and Bienenfeld linear/quadratic approximations from the 2002</t>
+          <t>the time-series content of the paper.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BEA 403-order matrix — are a **separate** empirical object (cross-</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sectional, 2002-only) deferred to v1.1 (see EPR §3).</t>
+          <t>The paper's Figures 1-9 — illustrative 403-sector Sraffa price-value</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>curves and Bienenfeld linear/quadratic approximations from the 2002</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>BEA 403-order matrix — are a **separate** empirical object (cross-</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sectional, 2002-only) deferred to v1.1 (see the companion Extension</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>Provenance Record, §3).</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>| XS2001-circ-* | 1947, 1958, 1963, 1967, 1972, 1998 | Shaikh (2020) Table 1 (circulating capital) | dimensionless ratio | `SalvagedInputs/book_data/Reconstructed/XS2001_aggregate_ratios.csv` |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>| XS2001-fixed-* | same 6 years | Shaikh (2020) Table 2 (fixed capital) | dimensionless ratio | same CSV |</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Underlying primary data: BEA Benchmark IO 1947-1972 (71-order) and 1998</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>(65-order), plus Shaikh (1998) Appendix 15.2 and Shaikh (2012) Data</t>
+          <t>| XS2001-circ-* | 1947, 1958, 1963, 1967, 1972, 1998 | Shaikh (2020) Table 1 (circulating capital) | dimensionless ratio | reconstructed CSV |</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Appendix for physical bundles. Per CHES adequacy: XS2001 and XS2101</t>
+          <t>| XS2001-fixed-* | same 6 years | Shaikh (2020) Table 2 (fixed capital) | dimensionless ratio | reconstructed CSV |</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>share this BEA-to-Sraffa pipeline (deferred shared module to v1.1).</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Subseries are named XS2001-circ-* (circulating-capital model) and</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>XS2001-fixed-* (fixed-capital model).</t>
         </is>
       </c>
     </row>
@@ -4476,213 +4476,213 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>For v1.0: direct ingestion of Tables 1-2 verbatim from the published</t>
+          <t>Underlying primary data: BEA Benchmark IO 1947-1972 (71-order) and 1998</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PDF. Each `(model, year, aggregate)` triple becomes one row; subseries</t>
+          <t>(65-order), plus Shaikh (1998) Appendix 15.2 and Shaikh (2012) Data</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>naming convention is `XS2001-{circ|fixed}-{aggregate_key}`.</t>
+          <t>Appendix for physical bundles. XS2001 and XS2101 share this</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BEA-to-Sraffa pipeline (the shared module is deferred to v1.1).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Paper window: 1947-1998 (6 sparse benchmark years per model). Extension</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>to additional BEA benchmark years (1977, 1982, 1987, 1992, 2002, 2007,</t>
+          <t>For v1.0: direct ingestion of Tables 1-2 verbatim from the published</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2012, 2017) deferred to v1.1 — requires shared BEA-to-Sraffa pipeline.</t>
+          <t>PDF. Each `(model, year, aggregate)` triple becomes one row; subseries</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>naming convention is `XS2001-{circ|fixed}-{aggregate_key}`.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>All ratios dimensionless. `r_obs` and `r_obs/R` are rates of profit</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>(decimal). The other 7 columns are price-aggregate / value-aggregate</t>
+          <t>Paper window: 1947-1998 (6 sparse benchmark years per model). Extension</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ratios in [0.94, 1.08].</t>
+          <t>to additional BEA benchmark years (1977, 1982, 1987, 1992, 2002, 2007,</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2012, 2017) deferred to v1.1 — requires shared BEA-to-Sraffa pipeline.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1. **Sparse benchmark years** (1947, 1958, 1963, 1967, 1972, 1998).</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Intermediate years not computed in the paper.</t>
+          <t>All ratios dimensionless. `r_obs` and `r_obs/R` are rates of profit</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2. **Matrix-size discontinuity**: 71-order for 1947-1972, 65-order for</t>
+          <t>(decimal). The other 7 columns are price-aggregate / value-aggregate</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1998. Documented as a column in the chopped CSV.</t>
+          <t>ratios in [0.94, 1.08].</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>3. The 1998 column in Table 2 has Rate of Profit = 0.98 and Max Rate</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">   R = 1.00 — the only sub-unit Max Rate in the panel; this is per</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the paper, not a transcription error.</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4. The paper's Figures 1-9 (403-sector cross-sectional curves) are</t>
+          <t>1. **Sparse benchmark years** (1947, 1958, 1963, 1967, 1972, 1998).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">   NOT in this series; see XS2001_EPR §3 for v1.1 plan.</t>
+          <t xml:space="preserve">   Intermediate years not computed in the paper.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2. **Matrix-size discontinuity**: 71-order for 1947-1972, 65-order for</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t xml:space="preserve">   1998. Documented as a column in the chopped CSV.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3. The 1998 column in Table 2 has Rate of Profit = 0.98 and Max Rate</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>- Dossier: `Technical/research/XS2001_research.json`</t>
+          <t xml:space="preserve">   R = 1.00 — the only sub-unit Max Rate in the panel; this is per</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>- Companion: `XS2101` (Shaikh-Coronado-Nassif-Pires 2020, 295-matrix</t>
+          <t xml:space="preserve">   the paper, not a transcription error.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CI distribution) — shares BEA-to-Sraffa pipeline</t>
+          <t>4. The paper's Figures 1-9 (403-sector cross-sectional curves) are</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>- Reconstructed: `SalvagedInputs/book_data/Reconstructed/XS2001_aggregate_ratios.csv`</t>
+          <t xml:space="preserve">   NOT in this series; see the Extension Provenance Record §3 for the</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>- Decision 0001 (ES scope)</t>
+          <t xml:space="preserve">   v1.1 plan.</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -4702,58 +4702,54 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>- Tolerance: 0.5% (verbatim transcription).</t>
+          <t>- Companion: `XS2101` (Shaikh-Coronado-Nassif-Pires 2020, 295-matrix</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Curvature Index distribution) — shares the BEA-to-Sraffa pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- Tolerance: 0.5% (verbatim transcription).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>- Compares processed parquet against the reconstructed CSV cell-by-cell.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4">
+    <row r="102">
+      <c r="A102" s="4">
         <f>== EPR: XS2001_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t># XS2001 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>**Series**: XS2001 — Shaikh (2020) Sraffa Price-Value Aggregates</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>**Construction**: `composite` (table verbatim + pipeline-derived in v1.1)</t>
-        </is>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t># XS2001 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4763,482 +4759,482 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>## 1. Extendability in principle</t>
+          <t>**Series**: XS2001 — Shaikh (2020) Sraffa Price-Value Aggregates</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>**Construction**: `composite` (table verbatim + pipeline-derived in v1.1)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>The paper's Tables 1-2 panel is sparse in time (6 benchmark years</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>1947-1998). Filling the missing BEA benchmark years (1977, 1982, 1987,</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1992, 2002, 2007, 2012, 2017) is methodologically straightforward: it</t>
+          <t>## 1. Extendability in principle</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>requires re-running the same Sraffa-aggregate computation (eqs 6, 8, 10</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>of the paper) on each missing benchmark IO matrix. The result would be</t>
+          <t>The paper's Tables 1-2 panel is sparse in time (6 benchmark years</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a near-quinquennial 1947-2017 time series of the SSE evidence.</t>
+          <t>1947-1998). Filling the missing BEA benchmark years (1977, 1982, 1987,</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1992, 2002, 2007, 2012, 2017) is methodologically straightforward: it</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>## 2. v1.0 scope</t>
+          <t>requires re-running the same Sraffa-aggregate computation (eqs 6, 8, 10</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>of the paper) on each missing benchmark input-output (IO) matrix. The</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Direct ingestion of Tables 1-2 verbatim. No extension years computed.</t>
+          <t>result would be a near-quinquennial 1947-2017 time series of the Sraffa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Validation compares processed parquet against the reconstructed CSV</t>
+          <t>Stochastic Effect (SSE) evidence.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>cell-by-cell.</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>## 2. v1.0 scope</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>## 3. v1.1 plan: shared BEA-to-Sraffa pipeline</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Direct ingestion of Tables 1-2 verbatim. No extension years computed.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHES adequacy explicitly recommends a shared</t>
+          <t>Validation compares processed parquet against the reconstructed CSV</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>`BEA_benchmark_IO_to_Sraffa_pipeline` module consumed by both XS2001</t>
+          <t>cell-by-cell.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>and XS2101. v1.1 implementation:</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>## 3. v1.1 plan: shared BEA-to-Sraffa pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>1. Build BEA Benchmark IO loader (Use/Make tables, 71/65/403/387-order</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">   per year).</t>
+          <t>A shared US Bureau of Economic Analysis (BEA) benchmark-IO-to-Sraffa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2. Apply paper-Appendix-1 exclusions (owner-occupied dwellings, scrap,</t>
+          <t>pipeline module should be consumed by both XS2001 and XS2101. v1.1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">   used/secondhand, non-comparable imports, RoW adjustment).</t>
+          <t>implementation:</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>3. Construct A matrix; compute H = A(I-A)^-1; solve eigenvalue R and</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">   left-eigenvector p(R).</t>
+          <t>1. Build BEA Benchmark IO loader (Use/Make tables, 71/65/403/387-order</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4. Compute Sraffa prices p(r) at r_obs; compute aggregate price-value</t>
+          <t xml:space="preserve">   per year).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ratios.</t>
+          <t>2. Apply paper-Appendix-1 exclusions (owner-occupied dwellings, scrap,</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5. Fill missing benchmark years 1977/1982/1987/1992/2002/2007/2012/2017.</t>
+          <t xml:space="preserve">   used/secondhand, non-comparable imports, RoW adjustment).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6. Regenerate Figures 1-9 (2002 403-sector price-value curves +</t>
+          <t>3. Construct A matrix; compute H = A(I-A)^-1; solve eigenvalue R and</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Bienenfeld linear/quadratic approximations) per equations 6, 8, 10.</t>
+          <t xml:space="preserve">   left-eigenvector p(R).</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4. Compute Sraffa prices p(r) at r_obs; compute aggregate price-value</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>This is a multi-day engineering effort and is explicitly deferred.</t>
+          <t xml:space="preserve">   ratios.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>5. Fill missing benchmark years 1977/1982/1987/1992/2002/2007/2012/2017.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>6. Regenerate Figures 1-9 (2002 403-sector price-value curves +</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Bienenfeld linear/quadratic approximations) per equations 6, 8, 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>This is a multi-day engineering effort and is explicitly deferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>## 4. Proxies</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>None. Tables 1-2 are the paper's own computed values.</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>## 5. Synthetic data</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>None. v1.0 is verbatim transcription only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>## 6. Conceptual continuity vs adjacent concepts</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr"/>
-    </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline) measures</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>`Sraffa aggregate price/value ratios at observed rates of profit` rather</t>
+          <t>None. v1.0 is verbatim transcription only.</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>than `nominal-vs-real GDP ratios` or `Marx-Tonak constant/variable</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>capital aggregates` because:</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>- Source agency choice: BEA Benchmark IO Use/Make tables are the input</t>
-        </is>
-      </c>
+      <c r="A154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">  to the paper's eqs 6, 8, 10. No alternative agency exists for the</t>
+          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline) measures</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">  industry-level technology matrix needed.</t>
+          <t>`Sraffa aggregate price/value ratios at observed rates of profit` rather</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>- Methodology continuity: the v1.0 verbatim Tables 1-2 panel and the</t>
+          <t>than `nominal-vs-real GDP ratios` or `Marx-Tonak constant/variable</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">  v1.1 extended panel both run *the same* eigenvalue/left-eigenvector</t>
+          <t>capital aggregates` because:</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">  computation on *the same* BEA-IO matrix family. Adding 1977/1982/.../2017</t>
+          <t>- Source agency choice: BEA Benchmark IO Use/Make tables are the input</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">  benchmark years is concept-identical, not concept-substituting.</t>
+          <t xml:space="preserve">  to the paper's eqs 6, 8, 10. No alternative agency exists for the</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>- Disambiguation: aggregate price/value ratios are NOT cross-sectional</t>
+          <t xml:space="preserve">  industry-level technology matrix needed.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sraffa price curves p(r) — those are XS2101's empirical object.</t>
+          <t>- Methodology continuity: the v1.0 verbatim Tables 1-2 panel and the</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tables 1-2 collapse the curve to a single scalar at r_obs per</t>
+          <t xml:space="preserve">  v1.1 extended panel both run *the same* eigenvalue/left-eigenvector</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (model, year). Extension preserves the scalar concept; the curve</t>
+          <t xml:space="preserve">  computation on *the same* BEA-IO matrix family. Adding 1977/1982/.../2017</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">  concept lives in a sibling series.</t>
+          <t xml:space="preserve">  benchmark years is concept-identical, not concept-substituting.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>- Disambiguation: aggregate price/value ratios are NOT cross-sectional</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>The book's original concept (Shaikh 2020 p. 9, "The Six Benchmark Year</t>
+          <t xml:space="preserve">  Sraffa price curves p(r) — those are XS2101's empirical object.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tables") was: "the close empirical correspondence between Sraffa prices</t>
+          <t xml:space="preserve">  Tables 1-2 collapse the curve to a single scalar at r_obs per</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>and labor values across the entire empirically observed range of the rate</t>
+          <t xml:space="preserve">  (model, year). Extension preserves the scalar concept; the curve</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>of profit". The modern series preserves the scalar aggregate-ratio</t>
+          <t xml:space="preserve">  concept lives in a sibling series.</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>computation while permitting matrix-order discontinuities (71-order</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>for 1947-1972, 65-order for 1998, 403/171-order for 2002+). This is NOT</t>
+          <t>The book's original concept (Shaikh 2020 p. 9, "The Six Benchmark Year</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>a proxy substitution forbidden by the No-Proxy rule because BEA IO is</t>
+          <t>Tables") was: "the close empirical correspondence between Sraffa prices</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>the canonical and only source of the input; extension years use exactly</t>
+          <t>and labor values across the entire empirically observed range of the rate</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>the same source family at successive vintages.</t>
+          <t>of profit". The modern series preserves the scalar aggregate-ratio</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>computation while permitting matrix-order discontinuities (71-order</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>## 7. Source-URL substitutions</t>
+          <t>for 1947-1972, 65-order for 1998, 403/171-order for 2002+). This is not</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>a proxy substitution because BEA IO is</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Per decision 0005 / CHES adequacy: `anwarshaikhecon.org` was DNS-</t>
+          <t>the canonical and only source of the input; extension years use exactly</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>unreachable 2026-05-18. The canonical URL-of-record for XS2001 is</t>
+          <t>the same source family at successive vintages.</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>the archival PDF at:</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>`Inputs/Capitalism Data/Technical/data/raw/01_SOURCE_MATERIALS/Web Folders/Shaikh Publications/[2020] Shaikh - An Empirically Sufficient Form for Sraffa Prices.pdf`</t>
+          <t>## 7. Source-URL substitutions</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5244,36 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Festschrift volume metadata per paper's own reference list (p. 20):</t>
+          <t>`anwarshaikhecon.org` was DNS-unreachable 2026-05-18. The canonical</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
+        <is>
+          <t>source-of-record for XS2001 is the archival PDF of Shaikh (2020),</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>"An Empirically Sufficient Form for Sraffa Prices".</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Festschrift volume metadata per paper's own reference list (p. 20):</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>Velupillai (ed.), Palgrave Macmillan. DOI pinning is a v1.1 task.</t>
         </is>
@@ -6162,7 +6182,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6291,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:51:41.933914+00:00</t>
+          <t>2026-07-02T06:33:10.693512+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS2001_extenbook.xlsx
+++ b/extenbooks/XS2001_extenbook.xlsx
@@ -4145,7 +4145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A189"/>
+  <dimension ref="A1:A193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -5268,14 +5268,42 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Festschrift volume metadata per paper's own reference list (p. 20):</t>
+          <t>Venue confirmed (F-2H-02, 2026-07-10): published as Shaikh (2024),</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Velupillai (ed.), Palgrave Macmillan. DOI pinning is a v1.1 task.</t>
+          <t>"An empirically sufficient form for Sraffa prices", Structural Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>and Economic Dynamics 69:1-9 (ScienceDirect PII S0954349X23001480).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>The "Velupillai (ed.), Palgrave Macmillan" string in the paper's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>p.20 reference list is a citation to a different Shaikh chapter, not</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>this paper's venue.</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6319,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:33:10.693512+00:00</t>
+          <t>2026-07-11T03:44:27.703700+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,11 +6334,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6333,6 +6361,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>study_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>study_replication</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "18 Sraffa-price test ratios (circulating- and fixed-capital normalizations) across 6 US BEA benchmark-IO years (1947-1998), all dimensionless ratios with uniform units. This is the verbatim aggregate-ratio content of Shaikh (2020) and renders sensibly as a multi-ratio panel. No units conflict; no truncation.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2001_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2001_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Decision 0001: ES placeholder. Phase 3 subagent must read the paper PDF, identify empirical figures, and either populate this placeholder as a single series OR expand to N series ES{group}01..ES{group}NN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dimensionless_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
